--- a/Rez-Weekly-Report.xlsx
+++ b/Rez-Weekly-Report.xlsx
@@ -23,7 +23,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A$1:$F$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,12 +31,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,15 +122,19 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00111111"/>
-      <sz val="11"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="11"/>
+      <color rgb="00444444"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="14">
@@ -199,7 +205,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -207,11 +213,16 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -283,13 +294,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -299,19 +313,47 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="168" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -323,6 +365,62 @@
         <patternFill patternType="solid">
           <fgColor rgb="00D9EAD3"/>
           <bgColor rgb="00D9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00006100"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9EAD3"/>
+          <bgColor rgb="00D9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBE4E4"/>
+          <bgColor rgb="00FBE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00006100"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9EAD3"/>
+          <bgColor rgb="00D9EAD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBE4E4"/>
+          <bgColor rgb="00FBE4E4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -420,9 +518,14 @@
     <author>Build Script</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Link this to the master week-ending date cell, or enter manually each Monday.</t>
+        <t>BEK purchases are company-wide (not per-location). This divides the total food purchases by 5 locations as an estimate. If BEK CSV has no 'Category' column, it sums all invoice line items divided by 5. For precise allocation, enter manually.</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>MANUAL ENTRY — v1: Enter total labor cost for this location from your Square Labor report (Total Hours x Avg Hourly Rate). Phase 2 will automate this via Square Labor CSV import. Example: if 80 hours @ avg $14.50/hr, enter 1160.</t>
       </text>
     </comment>
   </commentList>
@@ -435,9 +538,14 @@
     <author>Build Script</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Link this to the master week-ending date cell, or enter manually each Monday.</t>
+        <t>BEK purchases are company-wide (not per-location). This divides the total food purchases by 5 locations as an estimate. If BEK CSV has no 'Category' column, it sums all invoice line items divided by 5. For precise allocation, enter manually.</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>MANUAL ENTRY — v1: Enter total labor cost for this location from your Square Labor report (Total Hours x Avg Hourly Rate). Phase 2 will automate this via Square Labor CSV import. Example: if 80 hours @ avg $14.50/hr, enter 1160.</t>
       </text>
     </comment>
   </commentList>
@@ -452,7 +560,7 @@
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
-        <t>Enter the Sunday date of the week you are reporting (e.g., 2026-03-15). WoW comparison formulas reference this cell.</t>
+        <t>Enter the Sunday date for this reporting week (e.g., 2026-03-15). All calc tabs link to this cell, so WoW comparisons update automatically.</t>
       </text>
     </comment>
   </commentList>
@@ -540,9 +648,14 @@
     <author>Build Script</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Link this to the master week-ending date cell, or enter manually each Monday.</t>
+        <t>BEK purchases are company-wide (not per-location). This divides the total food purchases by 5 locations as an estimate. If BEK CSV has no 'Category' column, it sums all invoice line items divided by 5. For precise allocation, enter manually.</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>MANUAL ENTRY — v1: Enter total labor cost for this location from your Square Labor report (Total Hours x Avg Hourly Rate). Phase 2 will automate this via Square Labor CSV import. Example: if 80 hours @ avg $14.50/hr, enter 1160.</t>
       </text>
     </comment>
   </commentList>
@@ -555,9 +668,14 @@
     <author>Build Script</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Link this to the master week-ending date cell, or enter manually each Monday.</t>
+        <t>BEK purchases are company-wide (not per-location). This divides the total food purchases by 5 locations as an estimate. If BEK CSV has no 'Category' column, it sums all invoice line items divided by 5. For precise allocation, enter manually.</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>MANUAL ENTRY — v1: Enter total labor cost for this location from your Square Labor report (Total Hours x Avg Hourly Rate). Phase 2 will automate this via Square Labor CSV import. Example: if 80 hours @ avg $14.50/hr, enter 1160.</t>
       </text>
     </comment>
   </commentList>
@@ -570,9 +688,14 @@
     <author>Build Script</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Link this to the master week-ending date cell, or enter manually each Monday.</t>
+        <t>BEK purchases are company-wide (not per-location). This divides the total food purchases by 5 locations as an estimate. If BEK CSV has no 'Category' column, it sums all invoice line items divided by 5. For precise allocation, enter manually.</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>MANUAL ENTRY — v1: Enter total labor cost for this location from your Square Labor report (Total Hours x Avg Hourly Rate). Phase 2 will automate this via Square Labor CSV import. Example: if 80 hours @ avg $14.50/hr, enter 1160.</t>
       </text>
     </comment>
   </commentList>
@@ -869,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -896,323 +1019,357 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LABOR COST NOTE: The 'Est. Labor Cost (manual)' cell in each Location Calc tab requires manual entry for v1. Enter the total labor cost for that location from your Square Labor report each week. Labor Cost % is then computed automatically. Phase 2 will automate this via Square Labor CSV import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>WEEKLY CADENCE</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Every Monday morning: clear last week's data from each import tab (delete rows 3 and below — keep rows 1 and 2), paste new CSVs, then check the Summary tab.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>HOW TO EXPORT &amp; PASTE — SQUARE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>1. Log into Square Dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2. Go to: Reports &gt; Sales Summary</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>3. Select date range: Mon–Sun of the week you are reporting</t>
+          <t>1. Log into Square Dashboard</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>4. Click 'Export CSV'</t>
+          <t>2. Go to: Reports &gt; Sales Summary</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>5. Open the CSV, select all, copy</t>
+          <t>3. Select date range: Mon–Sun of the week you are reporting</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>6. Click into cell A3 of the Square-Import tab in this workbook</t>
+          <t>4. Click 'Export CSV'</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>5. Open the CSV, select all, copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6. Click into cell A3 of the Square-Import tab in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>7. Paste (do not paste with formatting — plain paste only)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>HOW TO EXPORT &amp; PASTE — DOORDASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>1. Log into DoorDash Merchant Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2. Go to: Financials &gt; Report Builder</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>3. Select the week you are reporting (Monday to Sunday)</t>
+          <t>1. Log into DoorDash Merchant Portal</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>4. Download CSV</t>
+          <t>2. Go to: Financials &gt; Report Builder</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>5. Open the CSV, select all, copy</t>
+          <t>3. Select the week you are reporting (Monday to Sunday)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>6. Click into cell A3 of the DoorDash-Import tab</t>
+          <t>4. Download CSV</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>5. Open the CSV, select all, copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>6. Click into cell A3 of the DoorDash-Import tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>7. Paste (plain paste only)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>HOW TO EXPORT &amp; PASTE — UBER EATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>1. Log into Uber Eats Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2. Go to: Analytics &gt; Reports</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>3. Select 'Download Report' and choose the reporting week</t>
+          <t>1. Log into Uber Eats Manager</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>4. Open the CSV, select all, copy</t>
+          <t>2. Go to: Analytics &gt; Reports</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>5. Click into cell A3 of the UberEats-Import tab</t>
+          <t>3. Select 'Download Report' and choose the reporting week</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>4. Open the CSV, select all, copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>5. Click into cell A3 of the UberEats-Import tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>6. Paste (plain paste only)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>HOW TO EXPORT &amp; PASTE — GRUBHUB</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>1. Log into Grubhub Restaurant Hub</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>2. Go to: Reports</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>3. Select the week and click 'Export'</t>
+          <t>1. Log into Grubhub Restaurant Hub</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>4. Open the CSV, select all, copy</t>
+          <t>2. Go to: Reports</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>5. Click into cell A3 of the Grubhub-Import tab</t>
+          <t>3. Select the week and click 'Export'</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>4. Open the CSV, select all, copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>5. Click into cell A3 of the Grubhub-Import tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>6. Paste (plain paste only)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="40" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>NOTE: Grubhub payouts are sometimes delayed 7–10 days. If the Grubhub column shows $0 on Monday, that is normal — check back Tuesday or Wednesday and update the Last Updated cell in the Grubhub-Import tab.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>HOW TO EXPORT &amp; PASTE — BEK ENTREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>1. Log into BEK Entree Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>2. Go to: Order History &gt; Export Invoice CSV</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>3. Select date range matching your reporting week</t>
+          <t>1. Log into BEK Entree Portal</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>4. Open the CSV, select all, copy</t>
+          <t>2. Go to: Order History &gt; Export Invoice CSV</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>5. Click into cell A3 of the BEK-Import tab</t>
+          <t>3. Select date range matching your reporting week</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>4. Open the CSV, select all, copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>5. Click into cell A3 of the BEK-Import tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>6. Paste (plain paste only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>TROUBLESHOOTING</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>If you see $0 or ERROR in the Summary tab, check the validation row (row 2) in each import tab. A red cell in row 2 means that column did not paste as a number — the data came in as text. Try pasting again without formatting, or paste into Notepad first and re-copy to strip formatting.</t>
+          <t>NOTE: BEK purchases are company-wide (not per-location). The workbook divides BEK total evenly across 5 locations as an estimate. For exact allocation, enter the per-location amount manually in the BEK Purchases cell of each Calc tab.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="2" t="inlineStr"/>
     </row>
-    <row r="54" ht="40" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>LABOR COST (MANUAL ENTRY — v1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>After pasting all CSV data: open each Location Calc tab and enter total labor cost for that location in the yellow 'Est. Labor Cost (manual)' cell. Get this number from your Square Labor report (Total Hours x Average Hourly Rate for that location). Labor Cost % is computed automatically once you enter the dollar amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>TROUBLESHOOTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>If you see $0 or ERROR in the Summary tab, check the validation row (row 2) in each import tab. A red cell in row 2 means that column did not paste as a number — the data came in as text. Try pasting again without formatting, or paste into Notepad first and re-copy to strip formatting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>If MATCH column errors (#N/A) appear, the column header in the import tab does not match the header in your CSV export. Update row 1 of the import tab to match the exact column name in your CSV file.</t>
         </is>
@@ -1233,10 +1390,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1256,7 +1413,10 @@
           <t>Week Ending:</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="B2" s="11">
+        <f>'Summary'!B2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="12" t="inlineStr">
@@ -1293,10 +1453,21 @@
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="28" t="n"/>
+      <c r="B5" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
+        <v/>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="27">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -1304,10 +1475,21 @@
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="27">
+        <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -1315,10 +1497,21 @@
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="27">
+        <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
+        <v/>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -1326,10 +1519,21 @@
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="27">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -1337,10 +1541,22 @@
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31" t="n"/>
+      <c r="B9" s="30">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),7),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="31">
+        <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -1349,95 +1565,198 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>BEK Purchases</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="E11" s="28" t="n"/>
-    </row>
+    <row r="11" ht="6" customHeight="1"/>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
+          <t>BEK Purchases</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="B13" s="28">
+        <f>IF(B9&gt;0,B12/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),8),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Estimated Labor Cost</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="E14" s="28" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Labor Cost %</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-    </row>
+    <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Est. Labor Cost (manual)</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
+          <t>Labor Cost %</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>IF(B9&gt;0,B16/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),9),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="28">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="E17" s="28" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="B20" s="33">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi Amarillo"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi Amarillo"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi Amarillo"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="33">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),10),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="33">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="28" t="n"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>[MMA] Formulas for This Week values will be added in Plan 02 — once CSV column names are validated with Rez's actual exports.</t>
+      <c r="B21" s="34">
+        <f>IF(B20&gt;0,B9/B20,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="34">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),11),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="34">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>[MMA] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21">
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -1450,10 +1769,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1473,7 +1792,10 @@
           <t>Week Ending:</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="B2" s="11">
+        <f>'Summary'!B2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="12" t="inlineStr">
@@ -1510,10 +1832,21 @@
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="28" t="n"/>
+      <c r="B5" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
+        <v/>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="27">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -1521,10 +1854,21 @@
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="27">
+        <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -1532,10 +1876,21 @@
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="27">
+        <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
+        <v/>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -1543,10 +1898,21 @@
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="27">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -1554,10 +1920,22 @@
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31" t="n"/>
+      <c r="B9" s="30">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),12),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="31">
+        <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -1566,95 +1944,198 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>BEK Purchases</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="E11" s="28" t="n"/>
-    </row>
+    <row r="11" ht="6" customHeight="1"/>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
+          <t>BEK Purchases</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="B13" s="28">
+        <f>IF(B9&gt;0,B12/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),13),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Estimated Labor Cost</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="E14" s="28" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Labor Cost %</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-    </row>
+    <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Est. Labor Cost (manual)</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
+          <t>Labor Cost %</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>IF(B9&gt;0,B16/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),14),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="28">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="E17" s="28" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="B20" s="33">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi 3rd"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi 3rd"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi 3rd"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="33">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),15),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="33">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="28" t="n"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>[MM3] Formulas for This Week values will be added in Plan 02 — once CSV column names are validated with Rez's actual exports.</t>
+      <c r="B21" s="34">
+        <f>IF(B20&gt;0,B9/B20,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="34">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),16),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="34">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>[MM3] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21">
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -1667,10 +2148,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1690,7 +2171,10 @@
           <t>Week Ending:</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="B2" s="11">
+        <f>'Summary'!B2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="12" t="inlineStr">
@@ -1727,10 +2211,21 @@
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="28" t="n"/>
+      <c r="B5" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
+        <v/>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="27">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -1738,10 +2233,21 @@
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="27">
+        <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -1749,10 +2255,21 @@
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="27">
+        <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
+        <v/>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -1760,10 +2277,21 @@
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="27">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -1771,10 +2299,22 @@
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31" t="n"/>
+      <c r="B9" s="30">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),17),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="31">
+        <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -1783,95 +2323,198 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>BEK Purchases</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="E11" s="28" t="n"/>
-    </row>
+    <row r="11" ht="6" customHeight="1"/>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
+          <t>BEK Purchases</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="B13" s="28">
+        <f>IF(B9&gt;0,B12/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),18),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Estimated Labor Cost</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="E14" s="28" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Labor Cost %</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-    </row>
+    <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Est. Labor Cost (manual)</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
+          <t>Labor Cost %</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>IF(B9&gt;0,B16/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),19),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="28">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="E17" s="28" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="B20" s="33">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Tikka Shack 1"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Tikka Shack 1"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Tikka Shack 1"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="33">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),20),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="33">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="28" t="n"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>[TS1] Formulas for This Week values will be added in Plan 02 — once CSV column names are validated with Rez's actual exports.</t>
+      <c r="B21" s="34">
+        <f>IF(B20&gt;0,B9/B20,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="34">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),21),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="34">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>[TS1] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21">
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -1884,10 +2527,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1907,7 +2550,10 @@
           <t>Week Ending:</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="B2" s="11">
+        <f>'Summary'!B2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="12" t="inlineStr">
@@ -1944,10 +2590,21 @@
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="28" t="n"/>
+      <c r="B5" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
+        <v/>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="27">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -1955,10 +2612,21 @@
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="27">
+        <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -1966,10 +2634,21 @@
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="27">
+        <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
+        <v/>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -1977,10 +2656,21 @@
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="27">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -1988,10 +2678,22 @@
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31" t="n"/>
+      <c r="B9" s="30">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),22),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="31">
+        <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -2000,95 +2702,198 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>BEK Purchases</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="E11" s="28" t="n"/>
-    </row>
+    <row r="11" ht="6" customHeight="1"/>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
+          <t>BEK Purchases</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="B13" s="28">
+        <f>IF(B9&gt;0,B12/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),23),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Estimated Labor Cost</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="E14" s="28" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Labor Cost %</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-    </row>
+    <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Est. Labor Cost (manual)</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
+          <t>Labor Cost %</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>IF(B9&gt;0,B16/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),24),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="28">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="E17" s="28" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="B20" s="33">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Tikka Shack 2"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Tikka Shack 2"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Tikka Shack 2"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="33">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),25),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="33">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="28" t="n"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>[TS2] Formulas for This Week values will be added in Plan 02 — once CSV column names are validated with Rez's actual exports.</t>
+      <c r="B21" s="34">
+        <f>IF(B20&gt;0,B9/B20,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="34">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),26),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="34">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>[TS2] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21">
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -2101,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2113,181 +2918,557 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Weekly Report Summary</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Week Ending:</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="B2" s="11" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="34" t="inlineStr"/>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr"/>
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Moto Medi Lubbock</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Moto Medi Amarillo</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Moto Medi 3rd</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>Tikka Shack 1</t>
         </is>
       </c>
-      <c r="F4" s="34" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Tikka Shack 2</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Net Revenue</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="37" t="n"/>
-      <c r="F5" s="37" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="B5" s="38">
+        <f>'MML-Calc'!B9</f>
+        <v/>
+      </c>
+      <c r="C5" s="38">
+        <f>'MMA-Calc'!B9</f>
+        <v/>
+      </c>
+      <c r="D5" s="38">
+        <f>'MM3-Calc'!B9</f>
+        <v/>
+      </c>
+      <c r="E5" s="39">
+        <f>'TS1-Calc'!B9</f>
+        <v/>
+      </c>
+      <c r="F5" s="39">
+        <f>'TS2-Calc'!B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="37" t="n"/>
-      <c r="F6" s="37" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="B6" s="41">
+        <f>'MML-Calc'!E9</f>
+        <v/>
+      </c>
+      <c r="C6" s="41">
+        <f>'MMA-Calc'!E9</f>
+        <v/>
+      </c>
+      <c r="D6" s="41">
+        <f>'MM3-Calc'!E9</f>
+        <v/>
+      </c>
+      <c r="E6" s="42">
+        <f>'TS1-Calc'!E9</f>
+        <v/>
+      </c>
+      <c r="F6" s="42">
+        <f>'TS2-Calc'!E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="37" t="n"/>
-      <c r="F7" s="37" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="B7" s="43">
+        <f>'MML-Calc'!B13</f>
+        <v/>
+      </c>
+      <c r="C7" s="43">
+        <f>'MMA-Calc'!B13</f>
+        <v/>
+      </c>
+      <c r="D7" s="43">
+        <f>'MM3-Calc'!B13</f>
+        <v/>
+      </c>
+      <c r="E7" s="44">
+        <f>'TS1-Calc'!B13</f>
+        <v/>
+      </c>
+      <c r="F7" s="44">
+        <f>'TS2-Calc'!B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="B8" s="41">
+        <f>'MML-Calc'!E13</f>
+        <v/>
+      </c>
+      <c r="C8" s="41">
+        <f>'MMA-Calc'!E13</f>
+        <v/>
+      </c>
+      <c r="D8" s="41">
+        <f>'MM3-Calc'!E13</f>
+        <v/>
+      </c>
+      <c r="E8" s="42">
+        <f>'TS1-Calc'!E13</f>
+        <v/>
+      </c>
+      <c r="F8" s="42">
+        <f>'TS2-Calc'!E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Labor Cost %</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="37" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="B9" s="43">
+        <f>'MML-Calc'!B17</f>
+        <v/>
+      </c>
+      <c r="C9" s="43">
+        <f>'MMA-Calc'!B17</f>
+        <v/>
+      </c>
+      <c r="D9" s="43">
+        <f>'MM3-Calc'!B17</f>
+        <v/>
+      </c>
+      <c r="E9" s="44">
+        <f>'TS1-Calc'!B17</f>
+        <v/>
+      </c>
+      <c r="F9" s="44">
+        <f>'TS2-Calc'!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="37" t="n"/>
-      <c r="F10" s="37" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="B10" s="41">
+        <f>'MML-Calc'!E17</f>
+        <v/>
+      </c>
+      <c r="C10" s="41">
+        <f>'MMA-Calc'!E17</f>
+        <v/>
+      </c>
+      <c r="D10" s="41">
+        <f>'MM3-Calc'!E17</f>
+        <v/>
+      </c>
+      <c r="E10" s="42">
+        <f>'TS1-Calc'!E17</f>
+        <v/>
+      </c>
+      <c r="F10" s="42">
+        <f>'TS2-Calc'!E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Order Volume</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="B11" s="45">
+        <f>'MML-Calc'!B20</f>
+        <v/>
+      </c>
+      <c r="C11" s="45">
+        <f>'MMA-Calc'!B20</f>
+        <v/>
+      </c>
+      <c r="D11" s="45">
+        <f>'MM3-Calc'!B20</f>
+        <v/>
+      </c>
+      <c r="E11" s="46">
+        <f>'TS1-Calc'!B20</f>
+        <v/>
+      </c>
+      <c r="F11" s="46">
+        <f>'TS2-Calc'!B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="37" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="B12" s="41">
+        <f>'MML-Calc'!E20</f>
+        <v/>
+      </c>
+      <c r="C12" s="41">
+        <f>'MMA-Calc'!E20</f>
+        <v/>
+      </c>
+      <c r="D12" s="41">
+        <f>'MM3-Calc'!E20</f>
+        <v/>
+      </c>
+      <c r="E12" s="42">
+        <f>'TS1-Calc'!E20</f>
+        <v/>
+      </c>
+      <c r="F12" s="42">
+        <f>'TS2-Calc'!E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Avg Ticket</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="B13" s="47">
+        <f>'MML-Calc'!B21</f>
+        <v/>
+      </c>
+      <c r="C13" s="47">
+        <f>'MMA-Calc'!B21</f>
+        <v/>
+      </c>
+      <c r="D13" s="47">
+        <f>'MM3-Calc'!B21</f>
+        <v/>
+      </c>
+      <c r="E13" s="48">
+        <f>'TS1-Calc'!B21</f>
+        <v/>
+      </c>
+      <c r="F13" s="48">
+        <f>'TS2-Calc'!B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>Formulas for all KPI cells will be added in Plan 02, after CSV column names are confirmed with Rez's real exports. Brand color bands: columns B-D = Moto Medi (orange), columns E-F = Tikka Shack (teal).</t>
+      <c r="B14" s="41">
+        <f>'MML-Calc'!E21</f>
+        <v/>
+      </c>
+      <c r="C14" s="41">
+        <f>'MMA-Calc'!E21</f>
+        <v/>
+      </c>
+      <c r="D14" s="41">
+        <f>'MM3-Calc'!E21</f>
+        <v/>
+      </c>
+      <c r="E14" s="42">
+        <f>'TS1-Calc'!E21</f>
+        <v/>
+      </c>
+      <c r="F14" s="42">
+        <f>'TS2-Calc'!E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="8" customHeight="1"/>
+    <row r="16" ht="8" customHeight="1"/>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="49" t="inlineStr">
+        <is>
+          <t>Purchase Cost % = BEK food purchases (company-wide, divided by 5 locations) / net revenue. Not true COGS — does not include inventory variance or waste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="49" t="inlineStr">
+        <is>
+          <t>Labor Cost % is estimated from manual entry in each Location Calc tab. Phase 2 automates this via Square Labor CSV import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>All delivery revenue (DoorDash, UberEats, Grubhub) uses net payout after platform fees/commissions.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A16:F16"/>
+  <mergeCells count="5">
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>'MML-Calc'!E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="4">
+      <formula>'MML-Calc'!E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>'MMA-Calc'!E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="4">
+      <formula>'MMA-Calc'!E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>'MM3-Calc'!E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="4">
+      <formula>'MM3-Calc'!E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="expression" priority="7" dxfId="3">
+      <formula>'TS1-Calc'!E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="4">
+      <formula>'TS1-Calc'!E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6">
+    <cfRule type="expression" priority="9" dxfId="3">
+      <formula>'TS2-Calc'!E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="4">
+      <formula>'TS2-Calc'!E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="expression" priority="11" dxfId="3">
+      <formula>'MML-Calc'!E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="4">
+      <formula>'MML-Calc'!E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" priority="13" dxfId="3">
+      <formula>'MMA-Calc'!E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="4">
+      <formula>'MMA-Calc'!E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" priority="15" dxfId="3">
+      <formula>'MM3-Calc'!E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="4">
+      <formula>'MM3-Calc'!E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="expression" priority="17" dxfId="3">
+      <formula>'TS1-Calc'!E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="4">
+      <formula>'TS1-Calc'!E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="expression" priority="19" dxfId="3">
+      <formula>'TS2-Calc'!E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="4">
+      <formula>'TS2-Calc'!E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" priority="21" dxfId="3">
+      <formula>'MML-Calc'!E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="22" dxfId="4">
+      <formula>'MML-Calc'!E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="expression" priority="23" dxfId="3">
+      <formula>'MMA-Calc'!E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" dxfId="4">
+      <formula>'MMA-Calc'!E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="expression" priority="25" dxfId="3">
+      <formula>'MM3-Calc'!E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="26" dxfId="4">
+      <formula>'MM3-Calc'!E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="expression" priority="27" dxfId="3">
+      <formula>'TS1-Calc'!E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="28" dxfId="4">
+      <formula>'TS1-Calc'!E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="expression" priority="29" dxfId="3">
+      <formula>'TS2-Calc'!E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="4">
+      <formula>'TS2-Calc'!E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" priority="31" dxfId="3">
+      <formula>'MML-Calc'!E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="32" dxfId="4">
+      <formula>'MML-Calc'!E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" priority="33" dxfId="3">
+      <formula>'MMA-Calc'!E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="34" dxfId="4">
+      <formula>'MMA-Calc'!E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="expression" priority="35" dxfId="3">
+      <formula>'MM3-Calc'!E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="4">
+      <formula>'MM3-Calc'!E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12">
+    <cfRule type="expression" priority="37" dxfId="3">
+      <formula>'TS1-Calc'!E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="38" dxfId="4">
+      <formula>'TS1-Calc'!E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="expression" priority="39" dxfId="3">
+      <formula>'TS2-Calc'!E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="40" dxfId="4">
+      <formula>'TS2-Calc'!E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="expression" priority="41" dxfId="3">
+      <formula>'MML-Calc'!E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="42" dxfId="4">
+      <formula>'MML-Calc'!E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" priority="43" dxfId="3">
+      <formula>'MMA-Calc'!E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="44" dxfId="4">
+      <formula>'MMA-Calc'!E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="expression" priority="45" dxfId="3">
+      <formula>'MM3-Calc'!E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="46" dxfId="4">
+      <formula>'MM3-Calc'!E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="expression" priority="47" dxfId="3">
+      <formula>'TS1-Calc'!E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="48" dxfId="4">
+      <formula>'TS1-Calc'!E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="expression" priority="49" dxfId="3">
+      <formula>'TS2-Calc'!E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="50" dxfId="4">
+      <formula>'TS2-Calc'!E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -7120,10 +8301,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -7143,7 +8324,10 @@
           <t>Week Ending:</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="B2" s="11">
+        <f>'Summary'!B2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="12" t="inlineStr">
@@ -7180,10 +8364,21 @@
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="28" t="n"/>
+      <c r="B5" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
+        <v/>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="27">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
@@ -7191,10 +8386,21 @@
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="28" t="n"/>
+      <c r="B6" s="27">
+        <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
@@ -7202,10 +8408,21 @@
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="28" t="n"/>
+      <c r="B7" s="27">
+        <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
+        <v/>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
@@ -7213,10 +8430,21 @@
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="28" t="n"/>
+      <c r="B8" s="27">
+        <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="27">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -7224,10 +8452,22 @@
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31" t="n"/>
+      <c r="B9" s="30">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),2),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="31">
+        <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
@@ -7236,95 +8476,198 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>BEK Purchases</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="E11" s="28" t="n"/>
-    </row>
+    <row r="11" ht="6" customHeight="1"/>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
+          <t>BEK Purchases</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="B13" s="28">
+        <f>IF(B9&gt;0,B12/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),3),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Estimated Labor Cost</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="E14" s="28" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Labor Cost %</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-    </row>
+    <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Est. Labor Cost (manual)</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
+          <t>Labor Cost %</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>IF(B9&gt;0,B16/B9,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),4),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="28">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="E17" s="28" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="B20" s="33">
+        <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi Lubbock"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi Lubbock"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi Lubbock"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="33">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),5),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="33">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="28" t="n"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>[MML] Formulas for This Week values will be added in Plan 02 — once CSV column names are validated with Rez's actual exports.</t>
+      <c r="B21" s="34">
+        <f>IF(B20&gt;0,B9/B20,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="34">
+        <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),6),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="34">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>[MML] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>E9&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>E9&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>E13&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>E13&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>E17&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>E17&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>E20&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>E20&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21">
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>E21&gt;0.05</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="2">
+      <formula>E21&lt;-0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/Rez-Weekly-Report.xlsx
+++ b/Rez-Weekly-Report.xlsx
@@ -21,6 +21,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TS1-Calc" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TS2-Calc" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labor-Import" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overtime-Tracker" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll-Output" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A$1:$F$20</definedName>
@@ -31,12 +34,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -222,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -262,11 +266,23 @@
     <xf numFmtId="164" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
@@ -278,9 +294,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -349,31 +362,32 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
     <dxf>
       <font>
         <name val="Calibri"/>
         <b val="1"/>
         <color rgb="00006100"/>
         <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9EAD3"/>
-          <bgColor rgb="00D9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="00006100"/>
-        <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -393,6 +407,34 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FBE4E4"/>
           <bgColor rgb="00FBE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="007F4F00"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFE0B2"/>
+          <bgColor rgb="00FFE0B2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00006100"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9EAD3"/>
+          <bgColor rgb="00D9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -421,6 +463,19 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FBE4E4"/>
           <bgColor rgb="00FBE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <color rgb="00006100"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9EAD3"/>
+          <bgColor rgb="00D9EAD3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -561,6 +616,66 @@
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>Enter the Sunday date for this reporting week (e.g., 2026-03-15). All calc tabs link to this cell, so WoW comparisons update automatically.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Build Script</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>PLACEHOLDER — update headers to match Rez's actual Square Labor export column names. After your first export, paste the real headers into row 2 of this tab so SUMIFS formulas in the Overtime-Tracker and Payroll-Output tabs resolve correctly.</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>This is the Employee Name column — used by Overtime-Tracker SUMIFS. Values must match the 'Square Name' column in Employee-Roster exactly (including capitalization and spacing).</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>Enter the date you pasted this data.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Build Script</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Enter Monday's date for this pay week. All daily hour columns reference this cell to determine which date to sum.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment15.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Build Script</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Enter the last day of the pay period.</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>Estimate only — does not include tips, deductions, or tax withholding. Verify against Gusto for actual payroll.</t>
       </text>
     </comment>
   </commentList>
@@ -992,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -1372,6 +1487,58 @@
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>If MATCH column errors (#N/A) appear, the column header in the import tab does not match the header in your CSV export. Update row 1 of the import tab to match the exact column name in your CSV file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>PAYROLL PREP (Phase 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>1. Paste Square Labor export into the Labor-Import tab (all locations in one paste — do NOT separate by location).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2. Set the Week Starting date on the Overtime-Tracker tab (cell B1) to the Monday of the pay week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>3. Review Overtime-Tracker for OT flags: red = 38+ hours (HIGH), yellow = 32-38 hours (WARN), green = under 32 hours. Pay close attention to employees working across multiple locations — their hours aggregate automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>4. Review Payroll-Output tab and export/copy to Gusto Smart Import. Column names are designed to match Gusto's auto-mapping fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>5. Update Employee Roster milestone dates (columns H-I) as employees reach milestones — Days Until Milestone (col J) and Status (col K) update automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>NOTE: Square Labor column headers in the Labor-Import tab are PLACEHOLDERS — update Labor-Import row 2 headers to match Rez's actual Square Labor export column names before using Overtime-Tracker formulas in production.</t>
         </is>
       </c>
     </row>
@@ -1401,14 +1568,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Moto Medi Amarillo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Week Ending:</t>
         </is>
@@ -1441,125 +1608,125 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Revenue Breakdown</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="30">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
         <v/>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="30">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="31">
         <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="30">
         <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
         <v/>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="30">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="31">
         <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="30">
         <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
         <v/>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="30">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="31">
         <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="30">
         <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
         <v/>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="30">
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="33">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),7),0)</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="33">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="34">
         <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Cost Metrics</t>
         </is>
@@ -1567,12 +1734,12 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>BEK Purchases</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="30">
         <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
         <v/>
       </c>
@@ -1581,30 +1748,30 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="31">
         <f>IF(B9&gt;0,B12/B9,0)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),8),0)</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="31">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="31">
         <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
@@ -1612,12 +1779,12 @@
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Est. Labor Cost (manual)</t>
         </is>
       </c>
-      <c r="B16" s="32" t="n">
+      <c r="B16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1625,30 +1792,30 @@
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Labor Cost %</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="31">
         <f>IF(B9&gt;0,B16/B9,0)</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),9),0)</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="31">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="31">
         <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
@@ -1656,53 +1823,53 @@
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="36">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi Amarillo"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi Amarillo"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi Amarillo"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi Amarillo"),0)</f>
         <v/>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="36">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),10),0)</f>
         <v/>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="36">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="31">
         <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="37">
         <f>IF(B20&gt;0,B9/B20,0)</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="37">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),11),0)</f>
         <v/>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="37">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="31">
         <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>[MMA] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
@@ -1718,42 +1885,42 @@
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule type="expression" priority="1" dxfId="3">
       <formula>E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="expression" priority="5" dxfId="1">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="expression" priority="7" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="3">
       <formula>E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="1">
       <formula>E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="expression" priority="9" dxfId="1">
+    <cfRule type="expression" priority="9" dxfId="3">
       <formula>E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="2">
+    <cfRule type="expression" priority="10" dxfId="1">
       <formula>E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1780,14 +1947,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Moto Medi 3rd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Week Ending:</t>
         </is>
@@ -1820,125 +1987,125 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Revenue Breakdown</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="30">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
         <v/>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="30">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="31">
         <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="30">
         <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
         <v/>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="30">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="31">
         <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="30">
         <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
         <v/>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="30">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="31">
         <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="30">
         <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
         <v/>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="30">
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="33">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),12),0)</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="33">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="34">
         <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Cost Metrics</t>
         </is>
@@ -1946,12 +2113,12 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>BEK Purchases</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="30">
         <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
         <v/>
       </c>
@@ -1960,30 +2127,30 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="31">
         <f>IF(B9&gt;0,B12/B9,0)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),13),0)</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="31">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="31">
         <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
@@ -1991,12 +2158,12 @@
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Est. Labor Cost (manual)</t>
         </is>
       </c>
-      <c r="B16" s="32" t="n">
+      <c r="B16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -2004,30 +2171,30 @@
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Labor Cost %</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="31">
         <f>IF(B9&gt;0,B16/B9,0)</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),14),0)</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="31">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="31">
         <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
@@ -2035,53 +2202,53 @@
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="36">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi 3rd"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi 3rd"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi 3rd"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi 3rd"),0)</f>
         <v/>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="36">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),15),0)</f>
         <v/>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="36">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="31">
         <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="37">
         <f>IF(B20&gt;0,B9/B20,0)</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="37">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),16),0)</f>
         <v/>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="37">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="31">
         <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>[MM3] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
@@ -2097,42 +2264,42 @@
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule type="expression" priority="1" dxfId="3">
       <formula>E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="expression" priority="5" dxfId="1">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="expression" priority="7" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="3">
       <formula>E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="1">
       <formula>E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="expression" priority="9" dxfId="1">
+    <cfRule type="expression" priority="9" dxfId="3">
       <formula>E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="2">
+    <cfRule type="expression" priority="10" dxfId="1">
       <formula>E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2159,14 +2326,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Tikka Shack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Week Ending:</t>
         </is>
@@ -2199,125 +2366,125 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Revenue Breakdown</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="30">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
         <v/>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="30">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="31">
         <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="30">
         <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
         <v/>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="30">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="31">
         <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="30">
         <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
         <v/>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="30">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="31">
         <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="30">
         <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
         <v/>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="30">
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="33">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),17),0)</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="33">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="34">
         <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Cost Metrics</t>
         </is>
@@ -2325,12 +2492,12 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>BEK Purchases</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="30">
         <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
         <v/>
       </c>
@@ -2339,30 +2506,30 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="31">
         <f>IF(B9&gt;0,B12/B9,0)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),18),0)</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="31">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="31">
         <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
@@ -2370,12 +2537,12 @@
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Est. Labor Cost (manual)</t>
         </is>
       </c>
-      <c r="B16" s="32" t="n">
+      <c r="B16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -2383,30 +2550,30 @@
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Labor Cost %</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="31">
         <f>IF(B9&gt;0,B16/B9,0)</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),19),0)</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="31">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="31">
         <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
@@ -2414,53 +2581,53 @@
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="36">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Tikka Shack 1"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Tikka Shack 1"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Tikka Shack 1"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Tikka Shack 1"),0)</f>
         <v/>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="36">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),20),0)</f>
         <v/>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="36">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="31">
         <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="37">
         <f>IF(B20&gt;0,B9/B20,0)</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="37">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),21),0)</f>
         <v/>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="37">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="31">
         <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>[TS1] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
@@ -2476,42 +2643,42 @@
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule type="expression" priority="1" dxfId="3">
       <formula>E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="expression" priority="5" dxfId="1">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="expression" priority="7" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="3">
       <formula>E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="1">
       <formula>E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="expression" priority="9" dxfId="1">
+    <cfRule type="expression" priority="9" dxfId="3">
       <formula>E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="2">
+    <cfRule type="expression" priority="10" dxfId="1">
       <formula>E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2538,14 +2705,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Tikka Shack 2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Week Ending:</t>
         </is>
@@ -2578,125 +2745,125 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Revenue Breakdown</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="30">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
         <v/>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="30">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="31">
         <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="30">
         <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
         <v/>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="30">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="31">
         <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="30">
         <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
         <v/>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="30">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="31">
         <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="30">
         <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
         <v/>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="30">
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="33">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),22),0)</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="33">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="34">
         <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Cost Metrics</t>
         </is>
@@ -2704,12 +2871,12 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>BEK Purchases</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="30">
         <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
         <v/>
       </c>
@@ -2718,30 +2885,30 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="31">
         <f>IF(B9&gt;0,B12/B9,0)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),23),0)</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="31">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="31">
         <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
@@ -2749,12 +2916,12 @@
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Est. Labor Cost (manual)</t>
         </is>
       </c>
-      <c r="B16" s="32" t="n">
+      <c r="B16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -2762,30 +2929,30 @@
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Labor Cost %</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="31">
         <f>IF(B9&gt;0,B16/B9,0)</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),24),0)</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="31">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="31">
         <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
@@ -2793,53 +2960,53 @@
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="36">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Tikka Shack 2"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Tikka Shack 2"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Tikka Shack 2"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Tikka Shack 2"),0)</f>
         <v/>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="36">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),25),0)</f>
         <v/>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="36">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="31">
         <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="37">
         <f>IF(B20&gt;0,B9/B20,0)</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="37">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),26),0)</f>
         <v/>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="37">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="31">
         <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>[TS2] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
@@ -2855,42 +3022,42 @@
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule type="expression" priority="1" dxfId="3">
       <formula>E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="expression" priority="5" dxfId="1">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="expression" priority="7" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="3">
       <formula>E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="1">
       <formula>E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="expression" priority="9" dxfId="1">
+    <cfRule type="expression" priority="9" dxfId="3">
       <formula>E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="2">
+    <cfRule type="expression" priority="10" dxfId="1">
       <formula>E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2918,14 +3085,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>Weekly Report Summary</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Week Ending:</t>
         </is>
@@ -2934,299 +3101,299 @@
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="37" t="inlineStr"/>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr"/>
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Moto Medi Lubbock</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>Moto Medi Amarillo</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>Moto Medi 3rd</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="40" t="inlineStr">
         <is>
           <t>Tikka Shack 1</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>Tikka Shack 2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Net Revenue</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="41">
         <f>'MML-Calc'!B9</f>
         <v/>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="41">
         <f>'MMA-Calc'!B9</f>
         <v/>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="41">
         <f>'MM3-Calc'!B9</f>
         <v/>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="42">
         <f>'TS1-Calc'!B9</f>
         <v/>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="42">
         <f>'TS2-Calc'!B9</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="44">
         <f>'MML-Calc'!E9</f>
         <v/>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="44">
         <f>'MMA-Calc'!E9</f>
         <v/>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="44">
         <f>'MM3-Calc'!E9</f>
         <v/>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="45">
         <f>'TS1-Calc'!E9</f>
         <v/>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="45">
         <f>'TS2-Calc'!E9</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="46">
         <f>'MML-Calc'!B13</f>
         <v/>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="46">
         <f>'MMA-Calc'!B13</f>
         <v/>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="46">
         <f>'MM3-Calc'!B13</f>
         <v/>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="47">
         <f>'TS1-Calc'!B13</f>
         <v/>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="47">
         <f>'TS2-Calc'!B13</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="44">
         <f>'MML-Calc'!E13</f>
         <v/>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="44">
         <f>'MMA-Calc'!E13</f>
         <v/>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="44">
         <f>'MM3-Calc'!E13</f>
         <v/>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="45">
         <f>'TS1-Calc'!E13</f>
         <v/>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="45">
         <f>'TS2-Calc'!E13</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Labor Cost %</t>
         </is>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="46">
         <f>'MML-Calc'!B17</f>
         <v/>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="46">
         <f>'MMA-Calc'!B17</f>
         <v/>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="46">
         <f>'MM3-Calc'!B17</f>
         <v/>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="47">
         <f>'TS1-Calc'!B17</f>
         <v/>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="47">
         <f>'TS2-Calc'!B17</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="44">
         <f>'MML-Calc'!E17</f>
         <v/>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="44">
         <f>'MMA-Calc'!E17</f>
         <v/>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="44">
         <f>'MM3-Calc'!E17</f>
         <v/>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="45">
         <f>'TS1-Calc'!E17</f>
         <v/>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="45">
         <f>'TS2-Calc'!E17</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Order Volume</t>
         </is>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="48">
         <f>'MML-Calc'!B20</f>
         <v/>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="48">
         <f>'MMA-Calc'!B20</f>
         <v/>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="48">
         <f>'MM3-Calc'!B20</f>
         <v/>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="49">
         <f>'TS1-Calc'!B20</f>
         <v/>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="49">
         <f>'TS2-Calc'!B20</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="44">
         <f>'MML-Calc'!E20</f>
         <v/>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="44">
         <f>'MMA-Calc'!E20</f>
         <v/>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="44">
         <f>'MM3-Calc'!E20</f>
         <v/>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="45">
         <f>'TS1-Calc'!E20</f>
         <v/>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="45">
         <f>'TS2-Calc'!E20</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Avg Ticket</t>
         </is>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="50">
         <f>'MML-Calc'!B21</f>
         <v/>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="50">
         <f>'MMA-Calc'!B21</f>
         <v/>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="50">
         <f>'MM3-Calc'!B21</f>
         <v/>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="51">
         <f>'TS1-Calc'!B21</f>
         <v/>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="51">
         <f>'TS2-Calc'!B21</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  WoW</t>
         </is>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="44">
         <f>'MML-Calc'!E21</f>
         <v/>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="44">
         <f>'MMA-Calc'!E21</f>
         <v/>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="44">
         <f>'MM3-Calc'!E21</f>
         <v/>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="45">
         <f>'TS1-Calc'!E21</f>
         <v/>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="45">
         <f>'TS2-Calc'!E21</f>
         <v/>
       </c>
@@ -3234,28 +3401,28 @@
     <row r="15" ht="8" customHeight="1"/>
     <row r="16" ht="8" customHeight="1"/>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="49" t="inlineStr">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>Purchase Cost % = BEK food purchases (company-wide, divided by 5 locations) / net revenue. Not true COGS — does not include inventory variance or waste.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="49" t="inlineStr">
+      <c r="A19" s="52" t="inlineStr">
         <is>
           <t>Labor Cost % is estimated from manual entry in each Location Calc tab. Phase 2 automates this via Square Labor CSV import.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="49" t="inlineStr">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>All delivery revenue (DoorDash, UberEats, Grubhub) uses net payout after platform fees/commissions.</t>
         </is>
@@ -3270,205 +3437,3062 @@
     <mergeCell ref="A20:F20"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="3">
+    <cfRule type="expression" priority="1" dxfId="4">
       <formula>'MML-Calc'!E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="4">
+    <cfRule type="expression" priority="2" dxfId="5">
       <formula>'MML-Calc'!E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="expression" priority="3" dxfId="3">
+    <cfRule type="expression" priority="3" dxfId="4">
       <formula>'MMA-Calc'!E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="4">
+    <cfRule type="expression" priority="4" dxfId="5">
       <formula>'MMA-Calc'!E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" priority="5" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="4">
       <formula>'MM3-Calc'!E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="4">
+    <cfRule type="expression" priority="6" dxfId="5">
       <formula>'MM3-Calc'!E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" priority="7" dxfId="3">
+    <cfRule type="expression" priority="7" dxfId="4">
       <formula>'TS1-Calc'!E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="4">
+    <cfRule type="expression" priority="8" dxfId="5">
       <formula>'TS1-Calc'!E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="expression" priority="9" dxfId="3">
+    <cfRule type="expression" priority="9" dxfId="4">
       <formula>'TS2-Calc'!E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="4">
+    <cfRule type="expression" priority="10" dxfId="5">
       <formula>'TS2-Calc'!E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="expression" priority="11" dxfId="3">
+    <cfRule type="expression" priority="11" dxfId="4">
       <formula>'MML-Calc'!E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" dxfId="4">
+    <cfRule type="expression" priority="12" dxfId="5">
       <formula>'MML-Calc'!E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="expression" priority="13" dxfId="3">
+    <cfRule type="expression" priority="13" dxfId="4">
       <formula>'MMA-Calc'!E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" dxfId="4">
+    <cfRule type="expression" priority="14" dxfId="5">
       <formula>'MMA-Calc'!E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" priority="15" dxfId="3">
+    <cfRule type="expression" priority="15" dxfId="4">
       <formula>'MM3-Calc'!E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" dxfId="4">
+    <cfRule type="expression" priority="16" dxfId="5">
       <formula>'MM3-Calc'!E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" priority="17" dxfId="3">
+    <cfRule type="expression" priority="17" dxfId="4">
       <formula>'TS1-Calc'!E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" dxfId="4">
+    <cfRule type="expression" priority="18" dxfId="5">
       <formula>'TS1-Calc'!E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="expression" priority="19" dxfId="3">
+    <cfRule type="expression" priority="19" dxfId="4">
       <formula>'TS2-Calc'!E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" dxfId="4">
+    <cfRule type="expression" priority="20" dxfId="5">
       <formula>'TS2-Calc'!E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="expression" priority="21" dxfId="3">
+    <cfRule type="expression" priority="21" dxfId="4">
       <formula>'MML-Calc'!E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" dxfId="4">
+    <cfRule type="expression" priority="22" dxfId="5">
       <formula>'MML-Calc'!E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" priority="23" dxfId="3">
+    <cfRule type="expression" priority="23" dxfId="4">
       <formula>'MMA-Calc'!E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" dxfId="4">
+    <cfRule type="expression" priority="24" dxfId="5">
       <formula>'MMA-Calc'!E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" priority="25" dxfId="3">
+    <cfRule type="expression" priority="25" dxfId="4">
       <formula>'MM3-Calc'!E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="26" dxfId="4">
+    <cfRule type="expression" priority="26" dxfId="5">
       <formula>'MM3-Calc'!E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="expression" priority="27" dxfId="3">
+    <cfRule type="expression" priority="27" dxfId="4">
       <formula>'TS1-Calc'!E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" dxfId="4">
+    <cfRule type="expression" priority="28" dxfId="5">
       <formula>'TS1-Calc'!E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10">
-    <cfRule type="expression" priority="29" dxfId="3">
+    <cfRule type="expression" priority="29" dxfId="4">
       <formula>'TS2-Calc'!E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" dxfId="4">
+    <cfRule type="expression" priority="30" dxfId="5">
       <formula>'TS2-Calc'!E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" priority="31" dxfId="3">
+    <cfRule type="expression" priority="31" dxfId="4">
       <formula>'MML-Calc'!E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="32" dxfId="4">
+    <cfRule type="expression" priority="32" dxfId="5">
       <formula>'MML-Calc'!E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" priority="33" dxfId="3">
+    <cfRule type="expression" priority="33" dxfId="4">
       <formula>'MMA-Calc'!E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" dxfId="4">
+    <cfRule type="expression" priority="34" dxfId="5">
       <formula>'MMA-Calc'!E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" priority="35" dxfId="3">
+    <cfRule type="expression" priority="35" dxfId="4">
       <formula>'MM3-Calc'!E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" dxfId="4">
+    <cfRule type="expression" priority="36" dxfId="5">
       <formula>'MM3-Calc'!E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12">
-    <cfRule type="expression" priority="37" dxfId="3">
+    <cfRule type="expression" priority="37" dxfId="4">
       <formula>'TS1-Calc'!E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="38" dxfId="4">
+    <cfRule type="expression" priority="38" dxfId="5">
       <formula>'TS1-Calc'!E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="expression" priority="39" dxfId="3">
+    <cfRule type="expression" priority="39" dxfId="4">
       <formula>'TS2-Calc'!E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="40" dxfId="4">
+    <cfRule type="expression" priority="40" dxfId="5">
       <formula>'TS2-Calc'!E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14">
-    <cfRule type="expression" priority="41" dxfId="3">
+    <cfRule type="expression" priority="41" dxfId="4">
       <formula>'MML-Calc'!E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="42" dxfId="4">
+    <cfRule type="expression" priority="42" dxfId="5">
       <formula>'MML-Calc'!E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" priority="43" dxfId="3">
+    <cfRule type="expression" priority="43" dxfId="4">
       <formula>'MMA-Calc'!E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="44" dxfId="4">
+    <cfRule type="expression" priority="44" dxfId="5">
       <formula>'MMA-Calc'!E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" priority="45" dxfId="3">
+    <cfRule type="expression" priority="45" dxfId="4">
       <formula>'MM3-Calc'!E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="46" dxfId="4">
+    <cfRule type="expression" priority="46" dxfId="5">
       <formula>'MM3-Calc'!E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="expression" priority="47" dxfId="3">
+    <cfRule type="expression" priority="47" dxfId="4">
       <formula>'TS1-Calc'!E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="48" dxfId="4">
+    <cfRule type="expression" priority="48" dxfId="5">
       <formula>'TS1-Calc'!E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" priority="49" dxfId="3">
+    <cfRule type="expression" priority="49" dxfId="4">
       <formula>'TS2-Calc'!E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="50" dxfId="4">
+    <cfRule type="expression" priority="50" dxfId="5">
       <formula>'TS2-Calc'!E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004A86C8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER HEADERS — Update row 2 to match your actual Square Labor CSV export column names exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Clock In</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Clock Out</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Regular Hours</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Overtime Hours</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>[Date — text/date]</t>
+        </is>
+      </c>
+      <c r="B3" s="7">
+        <f>IF(ISTEXT(INDEX(Labor-Import!A:Z,4,MATCH("Employee Name",Labor-Import!2:2,0))),"OK","CHECK - Employee Name should be text")</f>
+        <v/>
+      </c>
+      <c r="C3" s="7">
+        <f>IF(ISTEXT(INDEX(Labor-Import!A:Z,4,MATCH("Location",Labor-Import!2:2,0))),"OK","CHECK - Location should be text")</f>
+        <v/>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>[Clock In — text/date]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>[Clock Out — text/date]</t>
+        </is>
+      </c>
+      <c r="F3" s="7">
+        <f>IF(ISNUMBER(INDEX(Labor-Import!A:Z,4,MATCH("Regular Hours",Labor-Import!2:2,0))),"OK","PASTE ERROR - Regular Hours is not a number")</f>
+        <v/>
+      </c>
+      <c r="G3" s="7">
+        <f>IF(ISNUMBER(INDEX(Labor-Import!A:Z,4,MATCH("Overtime Hours",Labor-Import!2:2,0))),"OK","PASTE ERROR - Overtime Hours is not a number")</f>
+        <v/>
+      </c>
+      <c r="H3" s="7">
+        <f>IF(ISNUMBER(INDEX(Labor-Import!A:Z,4,MATCH("Total Hours",Labor-Import!2:2,0))),"OK","PASTE ERROR - Total Hours is not a number")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Marcus Johnson</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Ashley Torres</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Devon Scott</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Robert Kim</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Destiny Williams</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Jake Hernandez</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi 3rd</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Keisha Brown</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 2</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Jasmine Lee</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 2</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Marcus Johnson</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Marcus Johnson</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Ashley Torres</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Devon Scott</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Robert Kim</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Destiny Williams</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Jake Hernandez</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi 3rd</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Keisha Brown</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 2</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Marcus Johnson</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Ashley Torres</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Robert Kim</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Destiny Williams</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Jake Hernandez</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi 3rd</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Keisha Brown</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 2</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Jasmine Lee</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 2</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Marcus Johnson</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Marcus Johnson</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Ashley Torres</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Devon Scott</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Robert Kim</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Destiny Williams</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Jake Hernandez</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi 3rd</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Keisha Brown</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 2</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Marcus Johnson</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Ashley Torres</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Lubbock</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Robert Kim</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Destiny Williams</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Moto Medi Amarillo</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Jake Hernandez</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Moto Medi 3rd</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 1</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Keisha Brown</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Tikka Shack 2</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Jasmine Lee</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Tikka Shack 2</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Last Updated:</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>=A3="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>=B3="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>=C3="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="0">
+      <formula>=D3="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="0">
+      <formula>=E3="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="0">
+      <formula>=F3="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="0">
+      <formula>=G3="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="expression" priority="8" dxfId="0" stopIfTrue="0">
+      <formula>=H3="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F4A442"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Week Starting:</t>
+        </is>
+      </c>
+      <c r="B1" s="53" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>Weekly Total</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>Overtime Hrs</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>Regular Hrs</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Marcus Johnson</t>
+        </is>
+      </c>
+      <c r="B4" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A4,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C4" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A4,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D4" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A4,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E4" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A4,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A4,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A4,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H4" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A4,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I4" s="54">
+        <f>SUM(B4:H4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="54">
+        <f>MAX(I4-40,0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="54">
+        <f>MIN(I4,40)</f>
+        <v/>
+      </c>
+      <c r="L4" s="16">
+        <f>IF(I4&gt;=38,"HIGH",IF(I4&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Ashley Torres</t>
+        </is>
+      </c>
+      <c r="B5" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A5,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C5" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A5,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D5" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A5,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E5" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A5,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F5" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A5,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A5,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A5,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I5" s="55">
+        <f>SUM(B5:H5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="55">
+        <f>MAX(I5-40,0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="55">
+        <f>MIN(I5,40)</f>
+        <v/>
+      </c>
+      <c r="L5" s="20">
+        <f>IF(I5&gt;=38,"HIGH",IF(I5&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Devon Scott</t>
+        </is>
+      </c>
+      <c r="B6" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A6,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A6,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D6" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A6,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E6" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A6,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A6,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G6" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A6,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H6" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A6,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="54">
+        <f>SUM(B6:H6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="54">
+        <f>MAX(I6-40,0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="54">
+        <f>MIN(I6,40)</f>
+        <v/>
+      </c>
+      <c r="L6" s="16">
+        <f>IF(I6&gt;=38,"HIGH",IF(I6&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Robert Kim</t>
+        </is>
+      </c>
+      <c r="B7" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A7,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C7" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A7,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D7" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A7,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E7" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A7,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F7" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A7,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G7" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A7,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H7" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A7,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I7" s="55">
+        <f>SUM(B7:H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="55">
+        <f>MAX(I7-40,0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="55">
+        <f>MIN(I7,40)</f>
+        <v/>
+      </c>
+      <c r="L7" s="20">
+        <f>IF(I7&gt;=38,"HIGH",IF(I7&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Destiny Williams</t>
+        </is>
+      </c>
+      <c r="B8" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A8,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A8,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D8" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A8,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E8" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A8,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F8" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A8,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G8" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A8,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H8" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A8,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I8" s="54">
+        <f>SUM(B8:H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="54">
+        <f>MAX(I8-40,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="54">
+        <f>MIN(I8,40)</f>
+        <v/>
+      </c>
+      <c r="L8" s="16">
+        <f>IF(I8&gt;=38,"HIGH",IF(I8&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Jake Hernandez</t>
+        </is>
+      </c>
+      <c r="B9" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A9,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C9" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A9,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D9" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A9,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E9" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A9,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F9" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A9,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G9" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A9,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H9" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A9,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I9" s="55">
+        <f>SUM(B9:H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="55">
+        <f>MAX(I9-40,0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="55">
+        <f>MIN(I9,40)</f>
+        <v/>
+      </c>
+      <c r="L9" s="20">
+        <f>IF(I9&gt;=38,"HIGH",IF(I9&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="B10" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A10,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C10" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A10,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D10" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A10,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E10" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A10,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F10" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A10,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G10" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A10,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H10" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A10,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I10" s="54">
+        <f>SUM(B10:H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="54">
+        <f>MAX(I10-40,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="54">
+        <f>MIN(I10,40)</f>
+        <v/>
+      </c>
+      <c r="L10" s="16">
+        <f>IF(I10&gt;=38,"HIGH",IF(I10&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="B11" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A11,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C11" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A11,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D11" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A11,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E11" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A11,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F11" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A11,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G11" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A11,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H11" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A11,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I11" s="55">
+        <f>SUM(B11:H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="55">
+        <f>MAX(I11-40,0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="55">
+        <f>MIN(I11,40)</f>
+        <v/>
+      </c>
+      <c r="L11" s="20">
+        <f>IF(I11&gt;=38,"HIGH",IF(I11&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Keisha Brown</t>
+        </is>
+      </c>
+      <c r="B12" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A12,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C12" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A12,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D12" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A12,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E12" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A12,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F12" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A12,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G12" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A12,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H12" s="54">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A12,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I12" s="54">
+        <f>SUM(B12:H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="54">
+        <f>MAX(I12-40,0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="54">
+        <f>MIN(I12,40)</f>
+        <v/>
+      </c>
+      <c r="L12" s="16">
+        <f>IF(I12&gt;=38,"HIGH",IF(I12&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Jasmine Lee</t>
+        </is>
+      </c>
+      <c r="B13" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A13,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A13,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+1)</f>
+        <v/>
+      </c>
+      <c r="D13" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A13,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+2)</f>
+        <v/>
+      </c>
+      <c r="E13" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A13,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+3)</f>
+        <v/>
+      </c>
+      <c r="F13" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A13,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+4)</f>
+        <v/>
+      </c>
+      <c r="G13" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A13,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+5)</f>
+        <v/>
+      </c>
+      <c r="H13" s="55">
+        <f>SUMIFS(INDEX('Labor-Import'!A:Z,0,MATCH("Total Hours",'Labor-Import'!2:2,0)),INDEX('Labor-Import'!A:Z,0,MATCH("Employee Name",'Labor-Import'!2:2,0)),A13,INDEX('Labor-Import'!A:Z,0,MATCH("Date",'Labor-Import'!2:2,0)),B$1+6)</f>
+        <v/>
+      </c>
+      <c r="I13" s="55">
+        <f>SUM(B13:H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="55">
+        <f>MAX(I13-40,0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="55">
+        <f>MIN(I13,40)</f>
+        <v/>
+      </c>
+      <c r="L13" s="20">
+        <f>IF(I13&gt;=38,"HIGH",IF(I13&gt;=32,"WARN","OK"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I4:I100">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="1">
+      <formula>38</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>AND(I4&gt;=32,I4&lt;38)</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="6">
+      <formula>32</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L4:L100">
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>L4="HIGH"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="2">
+      <formula>L4="WARN"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="6">
+      <formula>L4="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F4A442"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Pay Period Ending:</t>
+        </is>
+      </c>
+      <c r="B1" s="53" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Regular Hours</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Overtime Hours</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Current Pay Rate</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Estimated Gross Pay</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Pay Period</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8">
+        <f>'Overtime-Tracker'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="54">
+        <f>'Overtime-Tracker'!K4</f>
+        <v/>
+      </c>
+      <c r="C4" s="54">
+        <f>'Overtime-Tracker'!J4</f>
+        <v/>
+      </c>
+      <c r="D4" s="23">
+        <f>IFERROR(VLOOKUP(A4,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E4" s="23">
+        <f>IFERROR((B4*D4)+(C4*D4*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="22">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9">
+        <f>'Overtime-Tracker'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="55">
+        <f>'Overtime-Tracker'!K5</f>
+        <v/>
+      </c>
+      <c r="C5" s="55">
+        <f>'Overtime-Tracker'!J5</f>
+        <v/>
+      </c>
+      <c r="D5" s="56">
+        <f>IFERROR(VLOOKUP(A5,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E5" s="56">
+        <f>IFERROR((B5*D5)+(C5*D5*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="57">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8">
+        <f>'Overtime-Tracker'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="54">
+        <f>'Overtime-Tracker'!K6</f>
+        <v/>
+      </c>
+      <c r="C6" s="54">
+        <f>'Overtime-Tracker'!J6</f>
+        <v/>
+      </c>
+      <c r="D6" s="23">
+        <f>IFERROR(VLOOKUP(A6,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E6" s="23">
+        <f>IFERROR((B6*D6)+(C6*D6*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="22">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9">
+        <f>'Overtime-Tracker'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="55">
+        <f>'Overtime-Tracker'!K7</f>
+        <v/>
+      </c>
+      <c r="C7" s="55">
+        <f>'Overtime-Tracker'!J7</f>
+        <v/>
+      </c>
+      <c r="D7" s="56">
+        <f>IFERROR(VLOOKUP(A7,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E7" s="56">
+        <f>IFERROR((B7*D7)+(C7*D7*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="57">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8">
+        <f>'Overtime-Tracker'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="54">
+        <f>'Overtime-Tracker'!K8</f>
+        <v/>
+      </c>
+      <c r="C8" s="54">
+        <f>'Overtime-Tracker'!J8</f>
+        <v/>
+      </c>
+      <c r="D8" s="23">
+        <f>IFERROR(VLOOKUP(A8,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E8" s="23">
+        <f>IFERROR((B8*D8)+(C8*D8*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="22">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9">
+        <f>'Overtime-Tracker'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="55">
+        <f>'Overtime-Tracker'!K9</f>
+        <v/>
+      </c>
+      <c r="C9" s="55">
+        <f>'Overtime-Tracker'!J9</f>
+        <v/>
+      </c>
+      <c r="D9" s="56">
+        <f>IFERROR(VLOOKUP(A9,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E9" s="56">
+        <f>IFERROR((B9*D9)+(C9*D9*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="57">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8">
+        <f>'Overtime-Tracker'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="54">
+        <f>'Overtime-Tracker'!K10</f>
+        <v/>
+      </c>
+      <c r="C10" s="54">
+        <f>'Overtime-Tracker'!J10</f>
+        <v/>
+      </c>
+      <c r="D10" s="23">
+        <f>IFERROR(VLOOKUP(A10,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E10" s="23">
+        <f>IFERROR((B10*D10)+(C10*D10*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9">
+        <f>'Overtime-Tracker'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="55">
+        <f>'Overtime-Tracker'!K11</f>
+        <v/>
+      </c>
+      <c r="C11" s="55">
+        <f>'Overtime-Tracker'!J11</f>
+        <v/>
+      </c>
+      <c r="D11" s="56">
+        <f>IFERROR(VLOOKUP(A11,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E11" s="56">
+        <f>IFERROR((B11*D11)+(C11*D11*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="57">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8">
+        <f>'Overtime-Tracker'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="54">
+        <f>'Overtime-Tracker'!K12</f>
+        <v/>
+      </c>
+      <c r="C12" s="54">
+        <f>'Overtime-Tracker'!J12</f>
+        <v/>
+      </c>
+      <c r="D12" s="23">
+        <f>IFERROR(VLOOKUP(A12,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E12" s="23">
+        <f>IFERROR((B12*D12)+(C12*D12*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="22">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9">
+        <f>'Overtime-Tracker'!A13</f>
+        <v/>
+      </c>
+      <c r="B13" s="55">
+        <f>'Overtime-Tracker'!K13</f>
+        <v/>
+      </c>
+      <c r="C13" s="55">
+        <f>'Overtime-Tracker'!J13</f>
+        <v/>
+      </c>
+      <c r="D13" s="56">
+        <f>IFERROR(VLOOKUP(A13,'Employee-Roster'!B:D,3,FALSE),"RATE NOT FOUND")</f>
+        <v/>
+      </c>
+      <c r="E13" s="56">
+        <f>IFERROR((B13*D13)+(C13*D13*1.5),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="57">
+        <f>$B$1</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -7626,7 +10650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7636,6 +10660,10 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7674,6 +10702,26 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Next Milestone Date</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Milestone Type</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Days Until Milestone</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>Milestone Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -7709,6 +10757,24 @@
           <t>Lead cook — Lubbock</t>
         </is>
       </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>90-Day Review</t>
+        </is>
+      </c>
+      <c r="J2" s="15">
+        <f>IFERROR(H2-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K2" s="16">
+        <f>IF(J2="","",IF(J2&lt;=0,"OVERDUE",IF(J2&lt;=30,"SOON","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -7726,10 +10792,10 @@
           <t>MML</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>2024-09-15</t>
         </is>
@@ -7743,6 +10809,16 @@
         <is>
           <t>Cross-trained on prep</t>
         </is>
+      </c>
+      <c r="H3" s="18" t="inlineStr"/>
+      <c r="I3" s="9" t="inlineStr"/>
+      <c r="J3" s="19">
+        <f>IFERROR(H3-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="20">
+        <f>IF(J3="","",IF(J3&lt;=0,"OVERDUE",IF(J3&lt;=30,"SOON","OK")))</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -7775,6 +10851,24 @@
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>6-Month Check-In</t>
+        </is>
+      </c>
+      <c r="J4" s="15">
+        <f>IFERROR(H4-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="16">
+        <f>IF(J4="","",IF(J4&lt;=0,"OVERDUE",IF(J4&lt;=30,"SOON","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -7792,10 +10886,10 @@
           <t>MMA</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="17" t="n">
         <v>15.75</v>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>2024-08-20</t>
         </is>
@@ -7806,6 +10900,24 @@
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Annual Review</t>
+        </is>
+      </c>
+      <c r="J5" s="19">
+        <f>IFERROR(H5-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="20">
+        <f>IF(J5="","",IF(J5&lt;=0,"OVERDUE",IF(J5&lt;=30,"SOON","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -7841,6 +10953,24 @@
           <t>Newer location</t>
         </is>
       </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Food Handler Cert</t>
+        </is>
+      </c>
+      <c r="J6" s="15">
+        <f>IFERROR(H6-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="16">
+        <f>IF(J6="","",IF(J6&lt;=0,"OVERDUE",IF(J6&lt;=30,"SOON","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -7858,10 +10988,10 @@
           <t>TS1</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
@@ -7875,6 +11005,24 @@
         <is>
           <t>Tikka Shack specialist</t>
         </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Annual Review</t>
+        </is>
+      </c>
+      <c r="J7" s="19">
+        <f>IFERROR(H7-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="20">
+        <f>IF(J7="","",IF(J7&lt;=0,"OVERDUE",IF(J7&lt;=30,"SOON","OK")))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -7907,6 +11055,24 @@
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>90-Day Pay Review</t>
+        </is>
+      </c>
+      <c r="J8" s="15">
+        <f>IFERROR(H8-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="16">
+        <f>IF(J8="","",IF(J8&lt;=0,"OVERDUE",IF(J8&lt;=30,"SOON","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -7924,10 +11090,10 @@
           <t>TS2</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="17" t="n">
         <v>14.25</v>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
@@ -7938,6 +11104,24 @@
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Annual Review</t>
+        </is>
+      </c>
+      <c r="J9" s="19">
+        <f>IFERROR(H9-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="20">
+        <f>IF(J9="","",IF(J9&lt;=0,"OVERDUE",IF(J9&lt;=30,"SOON","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -7973,6 +11157,16 @@
           <t>Part-time</t>
         </is>
       </c>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="15">
+        <f>IFERROR(H10-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="16">
+        <f>IF(J10="","",IF(J10&lt;=0,"OVERDUE",IF(J10&lt;=30,"SOON","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -7990,10 +11184,10 @@
           <t>TS2</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
@@ -8008,18 +11202,36 @@
           <t>Part-time</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>NOTE: 'Square Name' must match the employee name exactly as it appears in Square's clock-in export. This is the VLOOKUP key for labor cost calculations. Nicknames, capitalization, and spacing must match.</t>
+      <c r="H11" s="18" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr"/>
+      <c r="J11" s="19">
+        <f>IFERROR(H11-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="20">
+        <f>IF(J11="","",IF(J11&lt;=0,"OVERDUE",IF(J11&lt;=30,"SOON","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>NOTE: 'Square Name' must match the employee name exactly as it appears in Square's clock-in export. This is the VLOOKUP key for labor cost calculations. Nicknames, capitalization, and spacing must match. Milestone columns H-K: enter Next Milestone Date (col H) and Milestone Type (col I) manually; Days Until Milestone (col J) and Status (col K) update automatically via formula.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A13:K13"/>
   </mergeCells>
+  <conditionalFormatting sqref="J2:J100">
+    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
+      <formula>AND(J2&lt;&gt;"",J2&lt;=0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2" stopIfTrue="0">
+      <formula>AND(J2&gt;0,J2&lt;=30)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Location" error="Please select one of: MML,MMA,MM3,TS1,TS2" type="list">
       <formula1>"MML,MMA,MM3,TS1,TS2"</formula1>
@@ -8200,89 +11412,89 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n">
+      <c r="B2" s="23" t="n">
         <v>12050</v>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="24" t="n">
         <v>0.284</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="24" t="n">
         <v>0.312</v>
       </c>
-      <c r="E2" s="21" t="n">
+      <c r="E2" s="16" t="n">
         <v>387</v>
       </c>
-      <c r="F2" s="21" t="n">
+      <c r="F2" s="16" t="n">
         <v>19.1</v>
       </c>
-      <c r="G2" s="19" t="n">
+      <c r="G2" s="23" t="n">
         <v>9820</v>
       </c>
-      <c r="H2" s="20" t="n">
+      <c r="H2" s="24" t="n">
         <v>0.301</v>
       </c>
-      <c r="I2" s="20" t="n">
+      <c r="I2" s="24" t="n">
         <v>0.298</v>
       </c>
-      <c r="J2" s="21" t="n">
+      <c r="J2" s="16" t="n">
         <v>321</v>
       </c>
-      <c r="K2" s="21" t="n">
+      <c r="K2" s="16" t="n">
         <v>18.85</v>
       </c>
-      <c r="L2" s="19" t="n">
+      <c r="L2" s="23" t="n">
         <v>7640</v>
       </c>
-      <c r="M2" s="20" t="n">
+      <c r="M2" s="24" t="n">
         <v>0.318</v>
       </c>
-      <c r="N2" s="20" t="n">
+      <c r="N2" s="24" t="n">
         <v>0.305</v>
       </c>
-      <c r="O2" s="21" t="n">
+      <c r="O2" s="16" t="n">
         <v>258</v>
       </c>
-      <c r="P2" s="21" t="n">
+      <c r="P2" s="16" t="n">
         <v>18.92</v>
       </c>
-      <c r="Q2" s="19" t="n">
+      <c r="Q2" s="23" t="n">
         <v>6510</v>
       </c>
-      <c r="R2" s="20" t="n">
+      <c r="R2" s="24" t="n">
         <v>0.312</v>
       </c>
-      <c r="S2" s="20" t="n">
+      <c r="S2" s="24" t="n">
         <v>0.321</v>
       </c>
-      <c r="T2" s="21" t="n">
+      <c r="T2" s="16" t="n">
         <v>215</v>
       </c>
-      <c r="U2" s="21" t="n">
+      <c r="U2" s="16" t="n">
         <v>18.65</v>
       </c>
-      <c r="V2" s="19" t="n">
+      <c r="V2" s="23" t="n">
         <v>5890</v>
       </c>
-      <c r="W2" s="20" t="n">
+      <c r="W2" s="24" t="n">
         <v>0.296</v>
       </c>
-      <c r="X2" s="20" t="n">
+      <c r="X2" s="24" t="n">
         <v>0.334</v>
       </c>
-      <c r="Y2" s="21" t="n">
+      <c r="Y2" s="16" t="n">
         <v>182</v>
       </c>
-      <c r="Z2" s="21" t="n">
+      <c r="Z2" s="16" t="n">
         <v>18.88</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
@@ -8312,14 +11524,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>Moto Medi Lubbock</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Week Ending:</t>
         </is>
@@ -8352,125 +11564,125 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Revenue Breakdown</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Square Net Sales</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="30">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Net Sales",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
         <v/>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="30">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="31">
         <f>IF(C5&gt;0,(B5-C5)/C5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>DoorDash Net Revenue</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="30">
         <f>IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Net Payout",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
         <v/>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="30">
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="31">
         <f>IF(C6&gt;0,(B6-C6)/C6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>UberEats Net Revenue</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="30">
         <f>IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Net Payout",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
         <v/>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="30">
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="31">
         <f>IF(C7&gt;0,(B7-C7)/C7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Grubhub Net Revenue</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="30">
         <f>IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Net Payout",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
         <v/>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="30">
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>IF(C8&gt;0,(B8-C8)/C8,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Total Net Revenue</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="33">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),2),0)</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="33">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="34">
         <f>IF(C9&gt;0,(B9-C9)/C9,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Cost Metrics</t>
         </is>
@@ -8478,12 +11690,12 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>BEK Purchases</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="30">
         <f>IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Category",'BEK-Import'!1:1,0)),"Food",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,IFERROR(SUMIF(INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)),"&gt;0",INDEX('BEK-Import'!A:Z,0,MATCH("Total",'BEK-Import'!1:1,0)))/5,0))</f>
         <v/>
       </c>
@@ -8492,30 +11704,30 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Purchase Cost %</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="31">
         <f>IF(B9&gt;0,B12/B9,0)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),3),0)</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="31">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="31">
         <f>IF(C13&gt;0,(B13-C13)/C13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
@@ -8523,12 +11735,12 @@
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Est. Labor Cost (manual)</t>
         </is>
       </c>
-      <c r="B16" s="32" t="n">
+      <c r="B16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -8536,30 +11748,30 @@
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Labor Cost %</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="31">
         <f>IF(B9&gt;0,B16/B9,0)</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="31">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),4),0)</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="31">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="31">
         <f>IF(C17&gt;0,(B17-C17)/C17,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
@@ -8567,53 +11779,53 @@
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Total Orders</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="36">
         <f>IFERROR(SUMIFS(INDEX('Square-Import'!A:Z,0,MATCH("Order Count",'Square-Import'!1:1,0)),INDEX('Square-Import'!A:Z,0,MATCH("Location",'Square-Import'!1:1,0)),"Moto Medi Lubbock"),0)+IFERROR(SUMIFS(INDEX('DoorDash-Import'!A:Z,0,MATCH("Order Count",'DoorDash-Import'!1:1,0)),INDEX('DoorDash-Import'!A:Z,0,MATCH("Store Name",'DoorDash-Import'!1:1,0)),"Moto Medi Lubbock"),0)+IFERROR(SUMIFS(INDEX('UberEats-Import'!A:Z,0,MATCH("Trips",'UberEats-Import'!1:1,0)),INDEX('UberEats-Import'!A:Z,0,MATCH("Restaurant Name",'UberEats-Import'!1:1,0)),"Moto Medi Lubbock"),0)+IFERROR(SUMIFS(INDEX('Grubhub-Import'!A:Z,0,MATCH("Orders",'Grubhub-Import'!1:1,0)),INDEX('Grubhub-Import'!A:Z,0,MATCH("Restaurant",'Grubhub-Import'!1:1,0)),"Moto Medi Lubbock"),0)</f>
         <v/>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="36">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),5),0)</f>
         <v/>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="36">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="31">
         <f>IF(C20&gt;0,(B20-C20)/C20,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Avg Ticket Size</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="37">
         <f>IF(B20&gt;0,B9/B20,0)</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="37">
         <f>IFERROR(INDEX('Prior-Week'!A:Z,MATCH(B2-7,'Prior-Week'!A:A,0),6),0)</f>
         <v/>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="37">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="31">
         <f>IF(C21&gt;0,(B21-C21)/C21,0)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>[MML] Labor Cost requires manual entry — enter weekly labor total in the yellow B16 cell. Phase 2 automates via Square Labor CSV import (PAY-01).</t>
         </is>
@@ -8629,42 +11841,42 @@
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" priority="1" dxfId="1">
+    <cfRule type="expression" priority="1" dxfId="3">
       <formula>E9&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>E9&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>E13&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>E13&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="expression" priority="5" dxfId="1">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>E17&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>E17&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="expression" priority="7" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="3">
       <formula>E20&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="1">
       <formula>E20&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="expression" priority="9" dxfId="1">
+    <cfRule type="expression" priority="9" dxfId="3">
       <formula>E21&gt;0.05</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="2">
+    <cfRule type="expression" priority="10" dxfId="1">
       <formula>E21&lt;-0.05</formula>
     </cfRule>
   </conditionalFormatting>
